--- a/filer/25313763_arla.xlsx
+++ b/filer/25313763_arla.xlsx
@@ -4770,8 +4770,12 @@
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="E14" s="16" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>117000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
@@ -6515,7 +6519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6653,22 +6657,28 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:DividendsReceivedClassifiedAsOperatingActivities</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialAssets</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
+          <t>ifrs-full:DividendsReceivedClassifiedAsOperatingActivities</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>18000</v>
+      </c>
       <c r="G5" s="35" t="n">
-        <v>90000</v>
+        <v>24000</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>117000</v>
+        <v>21000</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -6684,23 +6694,25 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialLiabilities</t>
+          <t>ifrs-full:InvestmentsInSubsidiariesJointVenturesAndAssociates</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialLiabilities</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n">
-        <v>64000</v>
-      </c>
-      <c r="H6" s="38" t="n">
-        <v>22000</v>
-      </c>
+          <t>ifrs-full:InvestmentsInSubsidiariesJointVenturesAndAssociates</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>530000</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <v>565000</v>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>560000</v>
+      </c>
+      <c r="G6" s="38" t="n"/>
+      <c r="H6" s="38" t="n"/>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -6715,28 +6727,22 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsReceivedClassifiedAsOperatingActivities</t>
+          <t>ifrs-full:IssuedCapitalOrdinaryShares</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsReceivedClassifiedAsOperatingActivities</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>18000</v>
-      </c>
+          <t>ifrs-full:IssuedCapitalOrdinaryShares</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
       <c r="G7" s="35" t="n">
-        <v>24000</v>
+        <v>2230000</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>21000</v>
+        <v>2049000</v>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
@@ -6752,25 +6758,23 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:InvestmentsInSubsidiariesJointVenturesAndAssociates</t>
+          <t>ifrs-full:IssuedCapitalPreferenceShares</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:InvestmentsInSubsidiariesJointVenturesAndAssociates</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>530000</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>565000</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>560000</v>
-      </c>
-      <c r="G8" s="38" t="n"/>
-      <c r="H8" s="38" t="n"/>
+          <t>ifrs-full:IssuedCapitalPreferenceShares</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="38" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="38" t="n">
+        <v>570000</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>834000</v>
+      </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -6785,117 +6789,24 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IssuedCapitalOrdinaryShares</t>
+          <t>ifrs-full:ProceedsFromSalesOrMaturityOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IssuedCapitalOrdinaryShares</t>
+          <t>ifrs-full:ProceedsFromSalesOrMaturityOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
         </is>
       </c>
       <c r="D9" s="35" t="n"/>
       <c r="E9" s="35" t="n"/>
       <c r="F9" s="35" t="n"/>
       <c r="G9" s="35" t="n">
-        <v>2230000</v>
+        <v>56000</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>2049000</v>
+        <v>36000</v>
       </c>
       <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:IssuedCapitalPreferenceShares</t>
-        </is>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:IssuedCapitalPreferenceShares</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n">
-        <v>570000</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>834000</v>
-      </c>
-      <c r="I10" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromSalesOrMaturityOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromSalesOrMaturityOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n">
-        <v>56000</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <v>36000</v>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ShareOfOtherComprehensiveIncomeOfAssociatesAndJointVenturesAccountedForUsingEquityMethodThatWillBeReclassifiedToProfitOrLossBeforeTax</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ShareOfOtherComprehensiveIncomeOfAssociatesAndJointVenturesAccountedForUsingEquityMethodThatWillBeReclassifiedToProfitOrLossBeforeTax</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n">
-        <v>-9000</v>
-      </c>
-      <c r="H12" s="38" t="n">
-        <v>-107000</v>
-      </c>
-      <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/25313763_arla.xlsx
+++ b/filer/25313763_arla.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse t.kr.</t>
+          <t>Resultatopgørelse t.EUR</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1431,7 +1431,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>AKTIVER t.kr.</t>
+          <t>AKTIVER t.EUR</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -2525,7 +2525,7 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PASSIVER t.kr.</t>
+          <t>PASSIVER t.EUR</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -4174,7 +4174,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse &amp; nøgleoplysninger (t.kr.)</t>
+          <t>Resultatopgørelse &amp; nøgleoplysninger (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -4538,7 +4538,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Balance (t.kr.)</t>
+          <t>Balance (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -6368,15 +6368,15 @@
         </is>
       </c>
       <c r="B60" s="29">
-        <f>IF('balance_raw_25313763'!$F$23="","—",IF(ABS(B20-'balance_raw_25313763'!$F$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_25313763'!$F$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_25313763'!$F$23="","—",IF(ABS(B20-'balance_raw_25313763'!$F$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_25313763'!$F$23,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C60" s="29">
-        <f>IF('balance_raw_25313763'!$E$23="","—",IF(ABS(C20-'balance_raw_25313763'!$E$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_25313763'!$E$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_25313763'!$E$23="","—",IF(ABS(C20-'balance_raw_25313763'!$E$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_25313763'!$E$23,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D60" s="29">
-        <f>IF('balance_raw_25313763'!$D$23="","—",IF(ABS(D20-'balance_raw_25313763'!$D$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_25313763'!$D$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_25313763'!$D$23="","—",IF(ABS(D20-'balance_raw_25313763'!$D$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_25313763'!$D$23,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F60" s="25" t="inlineStr">
@@ -6392,15 +6392,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_25313763'!$F$47="","—",IF(ABS(B24-'balance_raw_25313763'!$F$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_25313763'!$F$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_25313763'!$F$47="","—",IF(ABS(B24-'balance_raw_25313763'!$F$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_25313763'!$F$47,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_25313763'!$E$47="","—",IF(ABS(C24-'balance_raw_25313763'!$E$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_25313763'!$E$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_25313763'!$E$47="","—",IF(ABS(C24-'balance_raw_25313763'!$E$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_25313763'!$E$47,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_25313763'!$D$47="","—",IF(ABS(D24-'balance_raw_25313763'!$D$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_25313763'!$D$47,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_25313763'!$D$47="","—",IF(ABS(D24-'balance_raw_25313763'!$D$47)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_25313763'!$D$47,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -6416,15 +6416,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -6440,15 +6440,15 @@
         </is>
       </c>
       <c r="B63" s="29">
-        <f>IF('res_raw_25313763'!$F$4="","—",IF(ABS(B7-'res_raw_25313763'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_25313763'!$F$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$F$4="","—",IF(ABS(B7-'res_raw_25313763'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_25313763'!$F$4,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C63" s="29">
-        <f>IF('res_raw_25313763'!$E$4="","—",IF(ABS(C7-'res_raw_25313763'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_25313763'!$E$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$E$4="","—",IF(ABS(C7-'res_raw_25313763'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_25313763'!$E$4,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF('res_raw_25313763'!$D$4="","—",IF(ABS(D7-'res_raw_25313763'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_25313763'!$D$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$D$4="","—",IF(ABS(D7-'res_raw_25313763'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_25313763'!$D$4,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
@@ -6464,15 +6464,15 @@
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw_25313763'!$F$9="","—",IF(ABS(B12-'res_raw_25313763'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw_25313763'!$F$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$F$9="","—",IF(ABS(B12-'res_raw_25313763'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw_25313763'!$F$9,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw_25313763'!$E$9="","—",IF(ABS(C12-'res_raw_25313763'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw_25313763'!$E$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$E$9="","—",IF(ABS(C12-'res_raw_25313763'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw_25313763'!$E$9,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw_25313763'!$D$9="","—",IF(ABS(D12-'res_raw_25313763'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw_25313763'!$D$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$D$9="","—",IF(ABS(D12-'res_raw_25313763'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw_25313763'!$D$9,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
@@ -6488,15 +6488,15 @@
         </is>
       </c>
       <c r="B65" s="29">
-        <f>IF('res_raw_25313763'!$F$14="","—",IF(ABS(B15-'res_raw_25313763'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw_25313763'!$F$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$F$14="","—",IF(ABS(B15-'res_raw_25313763'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw_25313763'!$F$14,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C65" s="29">
-        <f>IF('res_raw_25313763'!$E$14="","—",IF(ABS(C15-'res_raw_25313763'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw_25313763'!$E$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$E$14="","—",IF(ABS(C15-'res_raw_25313763'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw_25313763'!$E$14,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF('res_raw_25313763'!$D$14="","—",IF(ABS(D15-'res_raw_25313763'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw_25313763'!$D$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_25313763'!$D$14="","—",IF(ABS(D15-'res_raw_25313763'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw_25313763'!$D$14,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F65" s="25" t="inlineStr">

--- a/filer/25313763_arla.xlsx
+++ b/filer/25313763_arla.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/25313763_arla.xlsx
+++ b/filer/25313763_arla.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_25313763" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_25313763" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_25313763" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_25313763" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4146,6 +4147,148 @@
       </c>
       <c r="F85" s="13">
         <f>IFERROR($F$29/($F$51+$F$54)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B88" s="17">
+        <f>'pengestrom_raw_25313763'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C88" s="17">
+        <f>'pengestrom_raw_25313763'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D88" s="17">
+        <f>'pengestrom_raw_25313763'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E88" s="17">
+        <f>'pengestrom_raw_25313763'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F88" s="17">
+        <f>'pengestrom_raw_25313763'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B89" s="17">
+        <f>'pengestrom_raw_25313763'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C89" s="17">
+        <f>'pengestrom_raw_25313763'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D89" s="17">
+        <f>'pengestrom_raw_25313763'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E89" s="17">
+        <f>'pengestrom_raw_25313763'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F89" s="17">
+        <f>'pengestrom_raw_25313763'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B90" s="17">
+        <f>'pengestrom_raw_25313763'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C90" s="17">
+        <f>'pengestrom_raw_25313763'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D90" s="17">
+        <f>'pengestrom_raw_25313763'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E90" s="17">
+        <f>'pengestrom_raw_25313763'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F90" s="17">
+        <f>'pengestrom_raw_25313763'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B91" s="17">
+        <f>'pengestrom_raw_25313763'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C91" s="17">
+        <f>'pengestrom_raw_25313763'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D91" s="17">
+        <f>'pengestrom_raw_25313763'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E91" s="17">
+        <f>'pengestrom_raw_25313763'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F91" s="17">
+        <f>'pengestrom_raw_25313763'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B92">
+        <f>IF(ABS(('pengestrom_raw_25313763'!$B$2+'pengestrom_raw_25313763'!$B$3+'pengestrom_raw_25313763'!$B$4)-'pengestrom_raw_25313763'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25313763'!$B$2+'pengestrom_raw_25313763'!$B$3+'pengestrom_raw_25313763'!$B$4)-'pengestrom_raw_25313763'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C92">
+        <f>IF(ABS(('pengestrom_raw_25313763'!$C$2+'pengestrom_raw_25313763'!$C$3+'pengestrom_raw_25313763'!$C$4)-'pengestrom_raw_25313763'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25313763'!$C$2+'pengestrom_raw_25313763'!$C$3+'pengestrom_raw_25313763'!$C$4)-'pengestrom_raw_25313763'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D92">
+        <f>IF(ABS(('pengestrom_raw_25313763'!$D$2+'pengestrom_raw_25313763'!$D$3+'pengestrom_raw_25313763'!$D$4)-'pengestrom_raw_25313763'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25313763'!$D$2+'pengestrom_raw_25313763'!$D$3+'pengestrom_raw_25313763'!$D$4)-'pengestrom_raw_25313763'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E92">
+        <f>IF(ABS(('pengestrom_raw_25313763'!$E$2+'pengestrom_raw_25313763'!$E$3+'pengestrom_raw_25313763'!$E$4)-'pengestrom_raw_25313763'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25313763'!$E$2+'pengestrom_raw_25313763'!$E$3+'pengestrom_raw_25313763'!$E$4)-'pengestrom_raw_25313763'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F92">
+        <f>IF(ABS(('pengestrom_raw_25313763'!$F$2+'pengestrom_raw_25313763'!$F$3+'pengestrom_raw_25313763'!$F$4)-'pengestrom_raw_25313763'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_25313763'!$F$2+'pengestrom_raw_25313763'!$F$3+'pengestrom_raw_25313763'!$F$4)-'pengestrom_raw_25313763'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4194,322 +4337,322 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>11202000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>13793000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>13674000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>13770000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>15066000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n">
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n">
         <v>10803000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>12068000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>2380000</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>2648000</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>2780000</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>2967000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>2998000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n">
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n">
         <v>1824000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>1913000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n">
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n">
         <v>508000</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>535000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>110000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>162000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>113000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>48000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>135000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n">
         <v>118000</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>68000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n">
         <v>598000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>647000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>14000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>37000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>135000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>183000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>175000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>75000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>117000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>280000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>318000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>308000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>407000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>449000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>455000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>463000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>514000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>61000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>49000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>56000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>46000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>81000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>346000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>400000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>399000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>417000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>433000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>21307</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>21895</v>
       </c>
-      <c r="F17" s="16" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>452000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>373000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>445000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>557000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>570000</v>
       </c>
     </row>
@@ -4558,754 +4701,754 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n">
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n">
         <v>938000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>897000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>946000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>954000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>1010000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>269000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>287000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n">
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n">
         <v>3149000</v>
       </c>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n">
         <v>560000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>462000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>247000</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>247000</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>246000</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>24000</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>4668000</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>4611000</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>4788000</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>5354000</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>5366000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>1248000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>1772000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>1384000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>1635000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>1743000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>1007000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>1267000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>1145000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>1317000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>1247000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n">
         <v>90000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>117000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>21000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>22000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>23000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>31000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>23000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n">
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n">
         <v>266000</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>327000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>97000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>106000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>138000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>91000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>76000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>3145000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>4135000</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>3511000</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>3976000</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>4061000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>7813000</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>8746000</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>8299000</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>9330000</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>9427000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n">
         <v>44000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>-161000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>2910000</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>3168000</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>3052000</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>3072000</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <v>2950000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n">
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n">
         <v>101000</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>106000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>269000</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>189000</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>198000</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>166000</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>159000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>2113000</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>2640000</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>2650000</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>2808000</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>2990000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n">
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n">
         <v>1194000</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>1221000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>1445000</v>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>1597000</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>1425000</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>1433000</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="17" t="n">
         <v>1469000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>280000</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>301000</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>306000</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>365000</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="17" t="n">
         <v>370000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>2457000</v>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>2663000</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>2597000</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>3087000</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="17" t="n">
         <v>3102000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
+      <c r="B46" s="17" t="n">
         <v>4903000</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>5578000</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>5247000</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>6192000</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="F46" s="17" t="n">
         <v>6411000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>7813000</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>8746000</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>8299000</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>9330000</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>9427000</v>
       </c>
     </row>
@@ -5315,6 +5458,134 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.EUR)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>780000</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>184000</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1151000</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>652000</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>862000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-482000</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-443000</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-519000</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-887000</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-630000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-330000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>269000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-592000</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>186000</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-241000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>-32000</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6513,7 +6784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
